--- a/CO国試data/CO_questions_2023.xlsx
+++ b/CO国試data/CO_questions_2023.xlsx
@@ -545,12 +545,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>3</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>内分泌</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>血液、造血器</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1716,7 +1704,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1752,15 +1739,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1850,15 +1837,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1907,7 +1894,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1943,15 +1929,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>4</v>
       </c>
@@ -2041,15 +2027,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>4</v>
       </c>
@@ -2098,7 +2084,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>True</t>
@@ -2134,15 +2119,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2232,15 +2217,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2289,7 +2274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>True</t>
@@ -2325,15 +2309,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2382,7 +2366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2418,15 +2401,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2475,7 +2458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2511,15 +2493,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2568,7 +2550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2604,15 +2585,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2702,15 +2683,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>4</v>
       </c>
@@ -2760,7 +2741,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2796,15 +2776,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -2853,7 +2833,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2889,15 +2868,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2946,7 +2925,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2982,15 +2960,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3039,7 +3017,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3075,15 +3052,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3132,7 +3109,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3168,15 +3144,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>4</v>
       </c>
@@ -3225,7 +3201,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>True</t>
@@ -3261,15 +3236,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3318,7 +3293,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3357,12 +3331,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3411,7 +3385,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>True</t>
@@ -3447,15 +3420,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>1</v>
       </c>
@@ -3504,7 +3477,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3540,15 +3512,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3597,7 +3569,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3633,15 +3604,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3731,15 +3702,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3788,7 +3759,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3824,15 +3794,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3881,7 +3851,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3917,15 +3886,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3974,7 +3943,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -4010,15 +3978,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>3</v>
       </c>
@@ -4067,7 +4035,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4103,15 +4070,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4160,7 +4127,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4196,15 +4162,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4253,7 +4219,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4289,15 +4254,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4346,7 +4311,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>True</t>
@@ -4382,15 +4346,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4439,7 +4403,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>True</t>
@@ -4475,15 +4438,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4532,7 +4495,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4568,15 +4530,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>3</v>
       </c>
@@ -4626,7 +4588,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4665,12 +4626,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4719,7 +4680,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4755,15 +4715,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4812,7 +4772,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4848,15 +4807,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4905,7 +4864,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4941,15 +4899,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4998,7 +4956,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>True</t>
@@ -5034,15 +4991,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5091,7 +5048,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5127,15 +5083,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5184,7 +5140,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5220,15 +5175,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>4</v>
       </c>
@@ -5277,7 +5232,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5313,15 +5267,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5370,7 +5324,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>False</t>
@@ -5406,15 +5359,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5463,7 +5416,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>True</t>
@@ -5499,15 +5451,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5556,7 +5508,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5592,15 +5543,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5649,7 +5600,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5685,15 +5635,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5742,7 +5692,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5778,15 +5727,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5835,7 +5784,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>True</t>
@@ -5871,15 +5819,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5928,7 +5876,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5964,15 +5911,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6021,7 +5968,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6057,15 +6003,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>2</v>
       </c>
@@ -6114,7 +6060,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6150,15 +6095,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>2</v>
       </c>
@@ -6207,7 +6152,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6243,15 +6187,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6300,7 +6244,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6336,15 +6279,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6393,7 +6336,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6429,15 +6371,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6486,7 +6428,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6522,15 +6463,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6579,7 +6520,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6615,15 +6555,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6713,15 +6653,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6771,7 +6711,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>True</t>
@@ -6807,15 +6746,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6905,15 +6844,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -7003,15 +6942,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7101,15 +7040,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7199,15 +7138,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2</v>
       </c>
@@ -7257,7 +7196,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>False</t>
@@ -7293,15 +7231,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7351,7 +7289,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>False</t>
@@ -7387,15 +7324,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7445,7 +7382,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>True</t>
@@ -7481,15 +7417,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7579,15 +7515,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7636,7 +7572,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7672,15 +7607,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7729,7 +7664,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7768,12 +7702,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7822,7 +7756,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7858,15 +7791,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7915,7 +7848,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>True</t>
@@ -7951,15 +7883,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -8008,7 +7940,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8044,15 +7975,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8101,7 +8032,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8137,15 +8067,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8194,7 +8124,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>True</t>
@@ -8230,15 +8159,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>臨床心理</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8287,7 +8216,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8323,15 +8251,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>4</v>
       </c>
@@ -8380,7 +8308,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8416,15 +8343,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8473,7 +8400,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8509,15 +8435,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8566,7 +8492,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8602,15 +8527,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8700,15 +8625,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8757,7 +8682,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8793,15 +8717,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8850,7 +8774,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8886,15 +8809,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8943,7 +8866,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>True</t>
@@ -8979,15 +8901,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9036,7 +8958,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>True</t>
@@ -9072,15 +8993,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9129,7 +9050,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9165,15 +9085,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9222,7 +9142,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9258,15 +9177,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9315,7 +9234,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9351,15 +9269,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>5</v>
       </c>
@@ -9449,15 +9367,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9506,7 +9424,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9542,15 +9459,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9600,7 +9517,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9636,15 +9552,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9693,7 +9609,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>True</t>
@@ -9729,15 +9644,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>1</v>
       </c>
@@ -9786,7 +9701,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9822,15 +9736,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9879,7 +9793,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9915,15 +9828,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9972,7 +9885,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10008,15 +9920,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10066,7 +9978,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10105,12 +10016,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10159,7 +10070,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>True</t>
@@ -10195,15 +10105,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10252,7 +10162,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10288,15 +10197,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10386,15 +10295,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>4</v>
       </c>
@@ -10484,15 +10393,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10542,7 +10451,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10578,15 +10486,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10635,7 +10543,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10671,15 +10578,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10728,7 +10635,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10764,15 +10670,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10821,7 +10727,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10857,15 +10762,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10914,7 +10819,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10950,15 +10854,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -11007,7 +10911,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11043,15 +10946,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11100,7 +11003,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11136,15 +11038,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11234,15 +11136,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11291,7 +11193,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11327,15 +11228,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11384,7 +11285,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11420,15 +11320,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11477,7 +11377,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11513,15 +11412,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11570,7 +11469,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11606,15 +11504,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11663,7 +11561,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11699,15 +11596,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>3</v>
       </c>
@@ -11756,7 +11653,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11792,15 +11688,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11849,7 +11745,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11885,15 +11780,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11942,7 +11837,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11978,15 +11872,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -12035,7 +11929,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12071,15 +11964,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12128,7 +12021,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12164,15 +12056,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12221,7 +12113,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12257,15 +12148,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -12314,7 +12205,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12350,15 +12240,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12407,7 +12297,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12443,15 +12332,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>4</v>
       </c>
@@ -12500,7 +12389,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>True</t>
@@ -12536,15 +12424,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12593,7 +12481,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12629,15 +12516,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12686,7 +12573,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12722,15 +12608,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12779,7 +12665,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12815,15 +12700,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12872,7 +12757,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>True</t>
@@ -12908,15 +12792,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12965,7 +12849,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -13001,15 +12884,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -13058,7 +12941,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>True</t>
@@ -13094,15 +12976,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13151,7 +13033,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13187,15 +13068,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13244,7 +13125,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13280,15 +13160,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13337,7 +13217,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>True</t>
@@ -13373,15 +13252,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13430,7 +13309,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13466,15 +13344,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13523,7 +13401,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13559,15 +13436,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13616,7 +13493,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13652,15 +13528,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13710,7 +13586,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
           <t>False</t>
@@ -13746,15 +13621,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13804,7 +13679,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
           <t>True</t>
@@ -13840,15 +13714,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13938,15 +13812,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13996,7 +13870,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>False</t>
@@ -14032,15 +13905,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14130,15 +14003,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14228,15 +14101,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14326,15 +14199,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14424,15 +14297,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14523,15 +14396,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2023.xlsx
+++ b/CO国試data/CO_questions_2023.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>末梢神経の構造と機能</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>内分泌</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>内分泌</t>
+          <t>内分泌器官の構造と機能</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>血液、造血器</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>血液、造血器</t>
+          <t>血液、造血器の構造と機能</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>色覚検査</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3328,12 +3328,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視野検査</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3978,12 +3978,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4162,12 +4162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4438,12 +4438,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4899,12 +4899,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5911,12 +5911,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>患者と視能訓練士の関係</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>加齢、老化</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6555,12 +6555,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6653,12 +6653,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>色覚検査</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7231,12 +7231,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7417,12 +7417,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7607,12 +7607,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7699,12 +7699,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>リハビリテーションの考え方</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7883,12 +7883,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7975,12 +7975,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>視能矯正訓練の臨床心理概要</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8343,12 +8343,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8527,12 +8527,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8993,12 +8993,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>調節異常</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9459,12 +9459,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9920,12 +9920,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10105,12 +10105,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10197,12 +10197,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10295,12 +10295,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>画像検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10486,12 +10486,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10670,12 +10670,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10762,12 +10762,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>固視検査</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10946,12 +10946,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11038,12 +11038,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11136,12 +11136,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11228,12 +11228,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11320,12 +11320,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11412,12 +11412,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11504,12 +11504,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11596,12 +11596,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11688,12 +11688,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11872,12 +11872,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11964,12 +11964,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12056,12 +12056,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12424,12 +12424,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12516,12 +12516,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12700,12 +12700,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12884,12 +12884,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13068,12 +13068,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13160,12 +13160,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13252,12 +13252,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13344,12 +13344,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13436,12 +13436,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13621,12 +13621,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13714,12 +13714,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13812,12 +13812,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13905,12 +13905,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -14003,12 +14003,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14101,12 +14101,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14297,12 +14297,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14396,12 +14396,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2023.xlsx
+++ b/CO国試data/CO_questions_2023.xlsx
@@ -550,7 +550,6 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +641,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +732,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -826,7 +828,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -918,7 +919,11 @@
           <t>末梢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>脳神経（第Ⅰ〜Ⅻ脳神経）</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -1010,7 +1015,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>網膜電図〈ERG〉</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>3</v>
       </c>
@@ -1102,7 +1111,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1207,11 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>シナプス、神経伝達物質</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1286,7 +1303,11 @@
           <t>内分泌器官の構造と機能</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>副腎皮質</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1399,6 @@
           <t>血液、造血器の構造と機能</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1490,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1562,7 +1581,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1654,7 +1677,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1747,7 +1769,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1845,7 +1871,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1937,7 +1967,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>視覚誘発電位〈VEP〉</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>4</v>
       </c>
@@ -2035,7 +2069,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
@@ -2127,7 +2165,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2225,7 +2267,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2317,7 +2363,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2409,7 +2459,11 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>インシデント、アクシデントとレポート</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2501,7 +2555,11 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>限界フリッカ値〈CFF〉</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
@@ -2593,7 +2651,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2691,7 +2753,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
@@ -2784,7 +2850,11 @@
           <t>色覚検査</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>色覚検査表〈仮性同色表〉</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -2876,7 +2946,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2968,7 +3037,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3060,7 +3128,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3152,7 +3224,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>4</v>
       </c>
@@ -3244,7 +3315,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3336,7 +3406,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3428,7 +3497,11 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>遠見、近見視力検査</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
@@ -3520,7 +3593,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3612,7 +3684,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3710,7 +3786,11 @@
           <t>視野検査</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>動的、静的視野測定法（自動視野計を含む）</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3802,7 +3882,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3894,7 +3973,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3986,7 +4069,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
@@ -4078,7 +4165,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4170,7 +4256,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4262,7 +4352,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4354,7 +4448,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4446,7 +4544,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4538,7 +4640,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>3</v>
       </c>
@@ -4631,7 +4737,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4723,7 +4828,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4815,7 +4924,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4907,7 +5020,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4999,7 +5116,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5091,7 +5207,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5183,7 +5303,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>微小斜視弱視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>4</v>
       </c>
@@ -5275,7 +5399,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5367,7 +5495,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5459,7 +5591,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5551,7 +5682,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5643,7 +5778,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5735,7 +5869,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5827,7 +5965,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5919,7 +6061,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6011,7 +6152,6 @@
           <t>患者と視能訓練士の関係</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>2</v>
       </c>
@@ -6103,7 +6243,11 @@
           <t>加齢、老化</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>加齢による細胞と組織の変化</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
@@ -6195,7 +6339,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>光の性質、幾何光学</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6287,7 +6435,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6379,7 +6526,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6471,7 +6622,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6563,7 +6718,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6661,7 +6815,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6754,7 +6912,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6852,7 +7014,11 @@
           <t>色覚検査</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>アノマロスコープ</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6950,7 +7116,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7048,7 +7213,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7146,7 +7315,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2</v>
       </c>
@@ -7239,7 +7407,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7332,7 +7504,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7425,7 +7601,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7523,7 +7698,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7615,7 +7794,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7707,7 +7885,11 @@
           <t>リハビリテーションの考え方</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>国際生活機能分類〈ICF〉</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7799,7 +7981,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7891,7 +8072,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7983,7 +8163,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8075,7 +8254,11 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>脳（大脳、間脳、中脳、橋、延髄、小脳）</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8167,7 +8350,6 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8259,7 +8441,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H85" t="n">
         <v>4</v>
       </c>
@@ -8351,7 +8537,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8443,7 +8628,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>視覚心理学</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8535,7 +8724,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8633,7 +8826,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8725,7 +8917,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>他覚的屈折検査（波面収差解析を含む）</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8817,7 +9013,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8909,7 +9109,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9001,7 +9200,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>両眼共同運動、両眼離反運動</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9093,7 +9296,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9185,7 +9387,6 @@
           <t>調節異常</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9277,7 +9478,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>5</v>
       </c>
@@ -9375,7 +9580,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9467,7 +9671,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9560,7 +9768,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9652,7 +9859,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>1</v>
       </c>
@@ -9744,7 +9950,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9836,7 +10046,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9928,7 +10137,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>眼球電図〈EOG〉</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10021,7 +10234,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10113,7 +10325,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10205,7 +10416,6 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10303,7 +10513,11 @@
           <t>画像検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>超音波検査</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>4</v>
       </c>
@@ -10401,7 +10615,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10494,7 +10707,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10586,7 +10798,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10678,7 +10889,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>筋電図〈EMG〉</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10770,7 +10985,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10862,7 +11076,6 @@
           <t>固視検査</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10954,7 +11167,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11046,7 +11258,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11144,7 +11360,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11236,7 +11456,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11328,7 +11552,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11420,7 +11648,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11512,7 +11744,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>小児緑内障</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11604,7 +11840,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>3</v>
       </c>
@@ -11696,7 +11936,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>中心性漿液性脈絡網膜症</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11788,7 +12032,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11880,7 +12123,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -11972,7 +12219,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12064,7 +12310,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12156,7 +12406,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>微小斜視</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>4</v>
       </c>
@@ -12248,7 +12502,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12340,7 +12598,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>4</v>
       </c>
@@ -12432,7 +12694,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12524,7 +12785,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12616,7 +12876,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12708,7 +12967,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12800,7 +13063,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12892,7 +13159,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -12984,7 +13250,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13076,7 +13346,11 @@
           <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>大型弱視鏡検査</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13168,7 +13442,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13260,7 +13538,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13352,7 +13629,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13444,7 +13725,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13536,7 +13816,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13629,7 +13913,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13722,7 +14010,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>瞳孔不同</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13820,7 +14112,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13913,7 +14204,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14011,7 +14301,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14109,7 +14398,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14207,7 +14495,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14305,7 +14597,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14404,7 +14700,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2023.xlsx
+++ b/CO国試data/CO_questions_2023.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -689,10 +687,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -785,10 +781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -876,10 +870,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -972,10 +964,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1068,10 +1058,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1164,10 +1152,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1260,10 +1246,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,10 +1431,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1538,10 +1520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1634,10 +1614,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1726,10 +1704,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1828,10 +1804,8 @@
           <t>2023_co_23_am014.png</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1924,10 +1898,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2026,10 +1998,8 @@
           <t>2023_co_23_am016.png</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,10 +2194,8 @@
           <t>2023_co_23_am018.png</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2416,10 +2384,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2512,10 +2478,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2608,10 +2572,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2710,10 +2672,8 @@
           <t>2023_co_23_am023.png</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2807,10 +2767,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2994,10 +2952,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3085,10 +3041,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3181,10 +3135,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3272,10 +3224,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3363,10 +3313,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3454,10 +3402,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3550,10 +3496,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3641,10 +3585,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3743,10 +3685,8 @@
           <t>2023_co_23_am034（不備問題採点除外）.png</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3839,10 +3779,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3930,10 +3868,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4026,10 +3962,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4122,10 +4056,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4213,10 +4145,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4309,10 +4239,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4597,10 +4525,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4694,10 +4620,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4785,10 +4709,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4881,10 +4803,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4977,10 +4897,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5164,10 +5082,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5260,10 +5176,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5356,10 +5270,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5452,10 +5364,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5548,10 +5458,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5735,10 +5643,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5826,10 +5732,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5922,10 +5826,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6018,10 +5920,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6109,10 +6009,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6200,10 +6098,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6296,10 +6192,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6392,10 +6286,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6483,10 +6375,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6579,10 +6469,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6675,10 +6563,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6772,10 +6658,8 @@
           <t>2023_co_23_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6971,10 +6855,8 @@
           <t>2023_co_23_am068.jpg</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7073,10 +6955,8 @@
           <t>2023_co_23_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7364,10 +7244,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7461,10 +7339,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7751,10 +7627,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7842,10 +7716,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7938,10 +7810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8120,10 +7990,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8211,10 +8079,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8398,10 +8264,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8494,10 +8358,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8585,10 +8447,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8681,10 +8541,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8783,10 +8641,8 @@
           <t>2023_co_23_pm012.jpg</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8874,10 +8730,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8970,10 +8824,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9066,10 +8918,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9253,10 +9103,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9344,10 +9192,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9435,10 +9281,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9537,10 +9381,8 @@
           <t>2023_co_23_pm020.jpg</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9628,10 +9470,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9725,10 +9565,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9907,10 +9745,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10003,10 +9839,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10094,10 +9928,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10191,10 +10023,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10373,10 +10203,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10470,10 +10298,8 @@
           <t>2023_co_23_pm030.jpg</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10572,10 +10398,8 @@
           <t>2023_co_23_pm031.jpg</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10664,10 +10488,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10755,10 +10577,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10846,10 +10666,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10942,10 +10760,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11033,10 +10849,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11124,10 +10938,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11215,10 +11027,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11317,10 +11127,8 @@
           <t>2023_co_23_pm039.jpg</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11413,10 +11221,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11509,10 +11315,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11605,10 +11409,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11701,10 +11503,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11797,10 +11597,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11893,10 +11691,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11989,10 +11785,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12080,10 +11874,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12176,10 +11968,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12267,10 +12057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12363,10 +12151,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12459,10 +12245,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12555,10 +12339,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12742,10 +12524,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12833,10 +12613,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12924,10 +12702,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13116,10 +12892,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13399,10 +13173,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13586,10 +13358,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13682,10 +13452,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13773,10 +13541,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13870,10 +13636,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14069,10 +13833,8 @@
           <t>2023_co_23_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14161,10 +13923,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14355,10 +14115,8 @@
           <t>2023_co_23_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14452,10 +14210,8 @@
           <t>2023_co_23_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14554,10 +14310,8 @@
           <t>2023_co_23_pm073.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14657,10 +14411,8 @@
           <t>2023_co_23_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14759,10 +14511,8 @@
           <t>2023_co_23_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2023.xlsx
+++ b/CO国試data/CO_questions_2023.xlsx
@@ -1327,7 +1327,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1340,10 +1340,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S10" t="b">
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2079,7 +2077,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2092,10 +2090,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S18" t="b">
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2275,7 +2271,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2288,10 +2284,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S20" t="b">
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2848,7 +2842,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2861,10 +2855,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S26" t="b">
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3667,7 +3659,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3686,7 +3678,7 @@
         </is>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4320,7 +4312,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4333,10 +4325,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S42" t="b">
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4416,7 +4406,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4429,10 +4419,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4978,7 +4966,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4991,10 +4979,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S49" t="b">
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5534,7 +5520,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5547,10 +5533,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6740,7 +6724,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6753,10 +6737,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S68" t="b">
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7032,7 +7014,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7050,10 +7032,8 @@
           <t>2023_co_23_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7134,7 +7114,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7152,10 +7132,8 @@
           <t>2023_co_23_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S72" t="b">
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7421,7 +7399,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7434,10 +7412,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S75" t="b">
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7513,7 +7489,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -7531,10 +7507,8 @@
           <t>2023_co_23_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S76" t="b">
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7886,7 +7860,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7899,10 +7873,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S80" t="b">
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8160,7 +8132,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8173,10 +8145,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S83" t="b">
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8994,7 +8964,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -9007,10 +8977,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S92" t="b">
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9641,7 +9609,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9654,10 +9622,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S99" t="b">
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10099,7 +10065,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10112,10 +10078,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S104" t="b">
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12420,7 +12384,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12433,10 +12397,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S129" t="b">
+        <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12783,7 +12745,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -12796,10 +12758,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S133" t="b">
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -12968,7 +12928,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12981,10 +12941,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S135" t="b">
+        <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13064,7 +13022,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -13077,10 +13035,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13254,7 +13210,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -13267,10 +13223,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S138" t="b">
+        <v>1</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13718,7 +13672,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -13731,10 +13685,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S143" t="b">
+        <v>1</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14000,7 +13952,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -14018,10 +13970,8 @@
           <t>2023_co_23_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S146" t="b">
+        <v>1</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
